--- a/VerveStacks_SAU_grids_kan25/vt_vervestacks_SAU_v1.xlsx
+++ b/VerveStacks_SAU_grids_kan25/vt_vervestacks_SAU_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_SAU_grids_kan25\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1472081-18CB-4708-8F0A-9791BE3B1205}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8828683B-31BD-43E6-8474-7600C22E19B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E4624952-E1E7-43D2-90E6-AF391677F96D}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D57E8379-3D86-45ED-B40E-49D7AE79049D}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="4" r:id="rId1"/>
@@ -2704,7 +2704,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90D0AA7D-80E1-4A37-89EC-38F761E56DA7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4B146D5-28BA-4A80-9083-9679F9688E9A}">
   <dimension ref="B9:V176"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -7165,7 +7165,7 @@
         <v>16</v>
       </c>
       <c r="R81" t="s">
-        <v>715</v>
+        <v>645</v>
       </c>
       <c r="S81" t="s">
         <v>287</v>
@@ -7227,7 +7227,7 @@
         <v>16</v>
       </c>
       <c r="R82" t="s">
-        <v>645</v>
+        <v>715</v>
       </c>
       <c r="S82" t="s">
         <v>287</v>
@@ -13040,7 +13040,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B50732A3-14DD-436C-B9AA-7314AE6E1D74}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60AA1142-215E-4226-A828-4994B9AC02C7}">
   <dimension ref="B9:X31"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -14419,7 +14419,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C506AA3E-7539-4B3E-9647-D77071A016A2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7785C1F7-C52A-4AE2-84E4-3A2EDA2026B6}">
   <dimension ref="B9:X291"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -18778,7 +18778,7 @@
         <v>16</v>
       </c>
       <c r="T81" t="s">
-        <v>362</v>
+        <v>286</v>
       </c>
       <c r="U81" t="s">
         <v>287</v>
@@ -18843,7 +18843,7 @@
         <v>16</v>
       </c>
       <c r="T82" t="s">
-        <v>286</v>
+        <v>362</v>
       </c>
       <c r="U82" t="s">
         <v>287</v>
@@ -29542,7 +29542,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A1305F3-20EC-482C-A296-C53E0F08A3EF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E441A36B-0C29-42AE-8677-F257E20E7F14}">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData/>
